--- a/ig/nr-add-note/StructureDefinition-as-dr-person.xlsx
+++ b/ig/nr-add-note/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T09:13:24+00:00</t>
+    <t>2024-02-06T09:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-note/StructureDefinition-as-dr-person.xlsx
+++ b/ig/nr-add-note/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T09:15:22+00:00</t>
+    <t>2024-02-07T08:23:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
